--- a/outputs/evaluation/decision/v1/CF_M05/run_1/CF_M05_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/run_1/CF_M05_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,241 +471,529 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_AD07</t>
+          <t>CF_M05_AD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>*CF_M05_C15</t>
+          <t>CF_M05_C09 , *CF_M05_C11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU01</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Presentation and user experience</t>
+          <t>Integrity; Confidentiality</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Leader Microservice</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
+          <t>Aquest microservei té com a funció principal l’encaminament de totes les comunicacions cap al microservei corresponent dins de l’arquitectura del sistema.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.8676</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+          <t>*CF_M05_C11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Capacity; Maintainability; Scalability</t>
+          <t>Confidentiality</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>Access Control Microservice</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>This structure allows to develop, deploy, and scale each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
+          <t>El microservei Access Control té com a objectiu principal la gestió d’autenticació d’usuaris i els seus permisos dins de l’aplicació.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.7177</v>
+        <v>0.6817</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD10</t>
+          <t>CF_M05_AD05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M05_C14</t>
+          <t>*CF_M05_C13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_AU30, CF_M05_AU29</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maintainability</t>
+          <t>Traceability</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Angular; Spring Boot</t>
+          <t>Communication Log Microservice</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AD_09</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated. This structure clarifies roles, avoids unnecessary coupling, and facilitates testing, reusing, and maintaining the code over time.</t>
+          <t>El microservei Communication Log té com a finalitat principal registrar totes les comunicacions que es produeixen dins del sistema, tant entre microserveis com amb serveis externs.</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.7083</v>
+        <v>0.7118</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD11</t>
+          <t>CF_M05_AD06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CF_M05_C06, CF_M05_C07</t>
+          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_AU07</t>
+          <t>CF_M05_P05</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Availability; Capacity</t>
+          <t>Availability; Capacity; Access; Scalability</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Amazon EKS</t>
+          <t>Cloud Architecture</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>This structure allows to develop, deploy, and scale each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
+          <t>Pel desplegament de l’aplicació s’ha fet ús d’Amazon EKS, un servei que ofereix AWS el qual permet utilitzar Kubernetes (K8s), una plataforma d’orquestració de contenidors creada per Google, sense necessitat d’instal·lar-la ni mantenir-la.</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.6858</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>CF_M05_AD07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>*CF_M05_C15</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>61</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Presentation and user experience</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AD_12</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>L’aplicació segueix el patró Client-Servidor el qual organitza el codi en dos components diferenciats: el client, que formula sol·licituds de servei, i el servidor, que les rep, les processa i retorna respostes.</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.681</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CF_M05_AD08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>61</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Integrity; Security; Data persistence</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AD_12</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>L’aplicació segueix el patró Client-Servidor el qual organitza el codi en dos components diferenciats: el client, que formula sol·licituds de servei, i el servidor, que les rep, les processa i retorna respostes.</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CF_M05_AD09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>76</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Capacity; Maintainability; Scalability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Angular</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>En el present projecte, el client s’ha desenvolupat amb Angular, implementant una Single-PageApplication (SPA) que renderitza vistes dinàmiques i gestiona la navegació interna sense haver de recarregar la pàgina, millorant la fluïdesa d’ús.</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7027</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CF_M05_AD10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Angular; Spring Boot</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>En el present projecte, el client s’ha desenvolupat amb Angular, implementant una Single-PageApplication (SPA) que renderitza vistes dinàmiques i gestiona la navegació interna sense haver de recarregar la pàgina, millorant la fluïdesa d’ús.</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6516999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M05_AD11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>81</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Availability; Capacity</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>AD_11</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pel desplegament de l’aplicació s’ha fet ús d’Amazon EKS, un servei que ofereix AWS el qual permet utilitzar Kubernetes (K8s), una plataforma d’orquestració de contenidors creada per Google, sense necessitat d’instal·lar-la ni mantenir-la.</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6851</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M05_AD12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>78</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>AD_13</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Com ja s’ha pogut anar intuint en apartats anteriors, l’aplicació té una arquitectura basada en microserveis. Consisteix a dividir el sistema en un conjunt de serveis petits, independents i autònoms on cada microservei s’encarrega d’una funcionalitat específica i es comunica amb la resta mitjançant diversos sistemes de missatgeria.</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6586</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>CF_M05_AD13</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>*CF_M05_C18</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E12" t="n">
         <v>82</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Scalability</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Amazon EKS</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>This structure allows to develop, deploy, and scale each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.7635</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>En el present projecte, el client s’ha desenvolupat amb Angular, implementant una Single-PageApplication (SPA) que renderitza vistes dinàmiques i gestiona la navegació interna sense haver de recarregar la pàgina, millorant la fluïdesa d’ús.</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.636</v>
       </c>
     </row>
   </sheetData>
